--- a/assets/stocks.xlsx
+++ b/assets/stocks.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,10 +440,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>203.3654</v>
+        <v>222.9946665740097</v>
       </c>
       <c r="C2" t="n">
-        <v>738</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="3">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>220.89</v>
+        <v>232.3957245745405</v>
       </c>
       <c r="C7" t="n">
-        <v>1735</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="8">
@@ -613,6 +613,266 @@
       </c>
       <c r="C15" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CPPLUS.NS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2603.66</v>
+      </c>
+      <c r="C16" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CARTRADE.NS</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1876.22</v>
+      </c>
+      <c r="C17" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HFCL.NS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JAYBARMARU.NS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>164.69</v>
+      </c>
+      <c r="C19" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MTARTECH.NS</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4299.1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VENUSREM.NS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1719.95</v>
+      </c>
+      <c r="C21" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>VINCOFE.NS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>160</v>
+      </c>
+      <c r="C22" t="n">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VIYASH.NS</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>266.56</v>
+      </c>
+      <c r="C23" t="n">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>E2E.NS</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>423.6978</v>
+      </c>
+      <c r="C24" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EXICOM.NS</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FCL.NS</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>38.15</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IBULPP-E1.NS</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>105.8973</v>
+      </c>
+      <c r="C27" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>JSLL.NS</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>714.3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>KALAMANDIR.NS</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>151.4391</v>
+      </c>
+      <c r="C29" t="n">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>QPOWER.NS</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1003.5596</v>
+      </c>
+      <c r="C30" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RISHABH.NS</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>290.4923</v>
+      </c>
+      <c r="C31" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SAMMAANCAP.NS</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>152.1024</v>
+      </c>
+      <c r="C32" t="n">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SHREEREF-M.NS</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>315</v>
+      </c>
+      <c r="C33" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SUPREMEPWR-ST.NS</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>258.55</v>
+      </c>
+      <c r="C34" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>VAIBHAVGBL.NS</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/assets/stocks.xlsx
+++ b/assets/stocks.xlsx
@@ -761,7 +761,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IBULPP-E1.NS</t>
+          <t>SAMMAANCAP.NS</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -839,7 +839,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SHREEREF-M.NS</t>
+          <t>SHREEREF.BO</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -852,7 +852,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SUPREMEPWR-ST.NS</t>
+          <t>SUPREMEPWR.NS</t>
         </is>
       </c>
       <c r="B34" t="n">

--- a/assets/stocks.xlsx
+++ b/assets/stocks.xlsx
@@ -413,21 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Stock Name</t>
+          <t>Company Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Stock Code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Exchange</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Buying Price</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
@@ -436,443 +446,300 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>APOLLO.NS</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>222.9946665740097</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1439</v>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CCL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>961.5888</v>
+      </c>
+      <c r="E2" t="n">
+        <v>322</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCL.NS</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>961.5888</v>
-      </c>
-      <c r="C3" t="n">
-        <v>322</v>
+          <t>DEEDEV-T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DEEDEV-T</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>324</v>
+      </c>
+      <c r="E3" t="n">
+        <v>176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEEDEV.NS</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>324</v>
-      </c>
-      <c r="C4" t="n">
-        <v>351</v>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2303.0573</v>
+      </c>
+      <c r="E4" t="n">
+        <v>171</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GLAND.NS</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2243.7128</v>
-      </c>
-      <c r="C5" t="n">
-        <v>86</v>
+          <t>IDEAFORGE-T</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IDEAFORGE-T</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>711.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IDEAFORGE.NS</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>711.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>10</v>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>220.89</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3470</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JIOFIN.NS</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>232.3957245745405</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2938</v>
+          <t>JNKINDIA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JNKINDIA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>374.026225045372</v>
+      </c>
+      <c r="E7" t="n">
+        <v>551</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JNKINDIA.NS</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>410.45</v>
-      </c>
-      <c r="C8" t="n">
-        <v>100</v>
+          <t>JUSTDIAL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JUSTDIAL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>755.65</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JUSTDIAL.NS</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>755.65</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KPL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1698.7087</v>
+      </c>
+      <c r="E9" t="n">
+        <v>92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KPL.NS</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1698.7087</v>
-      </c>
-      <c r="C10" t="n">
-        <v>92</v>
+          <t>LOTUSCHO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LOTUSCHO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>351.8353</v>
+      </c>
+      <c r="E10" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LOTUSCHO.NS</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>351.8353</v>
-      </c>
-      <c r="C11" t="n">
-        <v>51</v>
+          <t>NYSSACORP-X</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NYSSACORP-X</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1023</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NYSSACORP.NS</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1023</v>
+          <t>SUPERHOUSE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SUPERHOUSE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>254.0205</v>
+      </c>
+      <c r="E12" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SUPERHOUSE.NS</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>254.0205</v>
-      </c>
-      <c r="C13" t="n">
-        <v>105</v>
+          <t>SWISSMLTRY-X</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SWISSMLTRY-X</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1050</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SWISSMLTRY.NS</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TATAELXSI.NS</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NSE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>576</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E14" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CPPLUS.NS</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2603.66</v>
-      </c>
-      <c r="C16" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CARTRADE.NS</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1876.22</v>
-      </c>
-      <c r="C17" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>HFCL.NS</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>80.14</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>JAYBARMARU.NS</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>164.69</v>
-      </c>
-      <c r="C19" t="n">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MTARTECH.NS</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>4299.1</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>VENUSREM.NS</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1719.95</v>
-      </c>
-      <c r="C21" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>VINCOFE.NS</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>160</v>
-      </c>
-      <c r="C22" t="n">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>VIYASH.NS</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>266.56</v>
-      </c>
-      <c r="C23" t="n">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>E2E.NS</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>423.6978</v>
-      </c>
-      <c r="C24" t="n">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>EXICOM.NS</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>176.5</v>
-      </c>
-      <c r="C25" t="n">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>FCL.NS</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>38.15</v>
-      </c>
-      <c r="C26" t="n">
-        <v>2501</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>SAMMAANCAP.NS</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>105.8973</v>
-      </c>
-      <c r="C27" t="n">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>JSLL.NS</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>714.3</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>KALAMANDIR.NS</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>151.4391</v>
-      </c>
-      <c r="C29" t="n">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>QPOWER.NS</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1003.5596</v>
-      </c>
-      <c r="C30" t="n">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>RISHABH.NS</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>290.4923</v>
-      </c>
-      <c r="C31" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>SAMMAANCAP.NS</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>152.1024</v>
-      </c>
-      <c r="C32" t="n">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SHREEREF.BO</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>315</v>
-      </c>
-      <c r="C33" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SUPREMEPWR.NS</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>258.55</v>
-      </c>
-      <c r="C34" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>VAIBHAVGBL.NS</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>250.5</v>
-      </c>
-      <c r="C35" t="n">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
